--- a/data/batch_fast_workbench/source_sheets/2店批量上品.xlsx
+++ b/data/batch_fast_workbench/source_sheets/2店批量上品.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -583,80 +583,80 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GTTY46VR?ie=UTF8&amp;ASIN=B0GTTY46VR&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GRH26ZBY?ie=UTF8&amp;ASIN=B0GRH26ZBY&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GTTY46VR.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GRH26ZBY.html</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GTTY46VR.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GRH26ZBY.html</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GRH26ZBY?ie=UTF8&amp;ASIN=B0GRH26ZBY&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FKM11PJW?ie=UTF8&amp;ASIN=B0FKM11PJW&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GRH26ZBY.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GRH26ZBY.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GVJDVHM3?ie=UTF8&amp;ASIN=B0GVJDVHM3&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GVYVJ5L6?ie=UTF8&amp;ASIN=B0GVYVJ5L6&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GVJDVHM3.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYVJ5L6.html</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GVJDVHM3.html</t>
+          <t>file:///Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FKM11PJW?ie=UTF8&amp;ASIN=B0FKM11PJW&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GVYMH961?ie=UTF8&amp;ASIN=B0GVYMH961&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYMH961.html</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
+          <t>file:///Users/admin/Desktop/competitor_html/store2/B0FKM11PJW.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GVYVJ5L6?ie=UTF8&amp;ASIN=B0GVYVJ5L6&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GS96JL5V?ie=UTF8&amp;ASIN=B0GS96JL5V&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYVJ5L6.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GS96JL5V.html</t>
         </is>
       </c>
       <c r="C7" s="23" t="n"/>
@@ -664,12 +664,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GVYMH961?ie=UTF8&amp;ASIN=B0GVYMH961&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GGBQ81WS?ie=UTF8&amp;ASIN=B0GGBQ81WS&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYMH961.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GGBQ81WS.html</t>
         </is>
       </c>
       <c r="C8" s="23" t="n"/>
@@ -677,12 +677,12 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GS96JL5V?ie=UTF8&amp;ASIN=B0GS96JL5V&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GQGJBRQF?ie=UTF8&amp;ASIN=B0GQGJBRQF&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GS96JL5V.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GQGJBRQF.html</t>
         </is>
       </c>
       <c r="C9" s="23" t="n"/>
@@ -690,12 +690,12 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GGBQ81WS?ie=UTF8&amp;ASIN=B0GGBQ81WS&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FCLS24NK?ie=UTF8&amp;ASIN=B0FCLS24NK&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GGBQ81WS.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FCLS24NK.html</t>
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
@@ -703,12 +703,12 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G5YYHCCW?ie=UTF8&amp;ASIN=B0G5YYHCCW&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FF9PTS3X?ie=UTF8&amp;ASIN=B0FF9PTS3X&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0G5YYHCCW.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FF9PTS3X.html</t>
         </is>
       </c>
       <c r="C11" s="23" t="n"/>
@@ -716,12 +716,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GQGJBRQF?ie=UTF8&amp;ASIN=B0GQGJBRQF&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FRLBGNNB?ie=UTF8&amp;ASIN=B0FRLBGNNB&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GQGJBRQF.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FRLBGNNB.html</t>
         </is>
       </c>
       <c r="C12" s="23" t="n"/>
@@ -729,12 +729,12 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GWMGBYFZ?ie=UTF8&amp;ASIN=B0GWMGBYFZ&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FCFLPGFV?ie=UTF8&amp;ASIN=B0FCFLPGFV&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GWMGBYFZ.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FCFLPGFV.html</t>
         </is>
       </c>
       <c r="C13" s="23" t="n"/>
@@ -742,12 +742,12 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FCLS24NK?ie=UTF8&amp;ASIN=B0FCLS24NK&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FFH8YLHP?ie=UTF8&amp;ASIN=B0FFH8YLHP&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FCLS24NK.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FFH8YLHP.html</t>
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
@@ -755,12 +755,12 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FF9PTS3X?ie=UTF8&amp;ASIN=B0FF9PTS3X&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FF4FSWCG?ie=UTF8&amp;ASIN=B0FF4FSWCG&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FF9PTS3X.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FF4FSWCG.html</t>
         </is>
       </c>
       <c r="C15" s="23" t="n"/>
@@ -768,12 +768,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GR5F9PCB?ie=UTF8&amp;ASIN=B0GR5F9PCB&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FKTD8P4T?ie=UTF8&amp;ASIN=B0FKTD8P4T&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GR5F9PCB.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FKTD8P4T.html</t>
         </is>
       </c>
       <c r="C16" s="23" t="n"/>
@@ -781,12 +781,12 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FRLBGNNB?ie=UTF8&amp;ASIN=B0FRLBGNNB&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GVYMLWC7?ie=UTF8&amp;ASIN=B0GVYMLWC7&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FRLBGNNB.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYMLWC7.html</t>
         </is>
       </c>
       <c r="C17" s="23" t="n"/>
@@ -794,12 +794,12 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GSF2RJTT?ie=UTF8&amp;ASIN=B0GSF2RJTT&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FH2FQHBX?ie=UTF8&amp;ASIN=B0FH2FQHBX&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GSF2RJTT.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FH2FQHBX.html</t>
         </is>
       </c>
       <c r="C18" s="23" t="n"/>
@@ -807,12 +807,12 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FCFLPGFV?ie=UTF8&amp;ASIN=B0FCFLPGFV&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GR4PKKRR?ie=UTF8&amp;ASIN=B0GR4PKKRR&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FCFLPGFV.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GR4PKKRR.html</t>
         </is>
       </c>
       <c r="C19" s="23" t="n"/>
@@ -820,12 +820,12 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FFH8YLHP?ie=UTF8&amp;ASIN=B0FFH8YLHP&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GQT8GC2M?ie=UTF8&amp;ASIN=B0GQT8GC2M&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FFH8YLHP.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GQT8GC2M.html</t>
         </is>
       </c>
       <c r="C20" s="23" t="n"/>
@@ -833,12 +833,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FF4FSWCG?ie=UTF8&amp;ASIN=B0FF4FSWCG&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0F4XK857G?ie=UTF8&amp;ASIN=B0F4XK857G&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FF4FSWCG.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0F4XK857G.html</t>
         </is>
       </c>
       <c r="C21" s="23" t="n"/>
@@ -846,12 +846,12 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FKTD8P4T?ie=UTF8&amp;ASIN=B0FKTD8P4T&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GQYM4Y1D?ie=UTF8&amp;ASIN=B0GQYM4Y1D&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FKTD8P4T.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GQYM4Y1D.html</t>
         </is>
       </c>
       <c r="C22" s="23" t="n"/>
@@ -859,12 +859,12 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GVYMLWC7?ie=UTF8&amp;ASIN=B0GVYMLWC7&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0FRMFLJ9R?ie=UTF8&amp;ASIN=B0FRMFLJ9R&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GVYMLWC7.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0FRMFLJ9R.html</t>
         </is>
       </c>
       <c r="C23" s="23" t="n"/>
@@ -872,12 +872,12 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FH2FQHBX?ie=UTF8&amp;ASIN=B0FH2FQHBX&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GHS8G18R?ie=UTF8&amp;ASIN=B0GHS8G18R&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FH2FQHBX.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GHS8G18R.html</t>
         </is>
       </c>
       <c r="C24" s="23" t="n"/>
@@ -885,12 +885,12 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GR4PKKRR?ie=UTF8&amp;ASIN=B0GR4PKKRR&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GGYPSFNJ?ie=UTF8&amp;ASIN=B0GGYPSFNJ&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GR4PKKRR.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GGYPSFNJ.html</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
@@ -898,12 +898,12 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GQT8GC2M?ie=UTF8&amp;ASIN=B0GQT8GC2M&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GR9H12MJ?ie=UTF8&amp;ASIN=B0GR9H12MJ&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GQT8GC2M.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GR9H12MJ.html</t>
         </is>
       </c>
       <c r="C26" s="23" t="n"/>
@@ -911,12 +911,12 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0F4XK857G?ie=UTF8&amp;ASIN=B0F4XK857G&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GSVJYRKD?ie=UTF8&amp;ASIN=B0GSVJYRKD&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0F4XK857G.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GSVJYRKD.html</t>
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
@@ -924,12 +924,12 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GQYM4Y1D?ie=UTF8&amp;ASIN=B0GQYM4Y1D&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GT4DC8K8?ie=UTF8&amp;ASIN=B0GT4DC8K8&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GQYM4Y1D.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GT4DC8K8.html</t>
         </is>
       </c>
       <c r="C28" s="23" t="n"/>
@@ -937,12 +937,12 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FRMFLJ9R?ie=UTF8&amp;ASIN=B0FRMFLJ9R&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GS5JGTDB?ie=UTF8&amp;ASIN=B0GS5JGTDB&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0FRMFLJ9R.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GS5JGTDB.html</t>
         </is>
       </c>
       <c r="C29" s="23" t="n"/>
@@ -950,190 +950,78 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GHS8G18R?ie=UTF8&amp;ASIN=B0GHS8G18R&amp;s=bazaar</t>
+          <t>https://www.amazon.com/dp/B0GWM1BPKM?ie=UTF8&amp;ASIN=B0GWM1BPKM&amp;s=bazaar</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GHS8G18R.html</t>
+          <t>/Users/admin/Desktop/competitor_html/store2/B0GWM1BPKM.html</t>
         </is>
       </c>
       <c r="C30" s="23" t="n"/>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GGYPSFNJ?ie=UTF8&amp;ASIN=B0GGYPSFNJ&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GGYPSFNJ.html</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GR9H12MJ?ie=UTF8&amp;ASIN=B0GR9H12MJ&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GR9H12MJ.html</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GSVJYRKD?ie=UTF8&amp;ASIN=B0GSVJYRKD&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GSVJYRKD.html</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GT4DC8K8?ie=UTF8&amp;ASIN=B0GT4DC8K8&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GT4DC8K8.html</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GS5JGTDB?ie=UTF8&amp;ASIN=B0GS5JGTDB&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GS5JGTDB.html</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GWM1BPKM?ie=UTF8&amp;ASIN=B0GWM1BPKM&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GWM1BPKM.html</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GS9WWQ2B?ie=UTF8&amp;ASIN=B0GS9WWQ2B&amp;s=bazaar</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>/Users/admin/Desktop/competitor_html/store2/B0GS9WWQ2B.html</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="n"/>
-    </row>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>